--- a/AAII_Financials/Yearly/AR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AR_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>31400</v>
+        <v>35800</v>
       </c>
       <c r="E14" s="3">
         <v>5900</v>
@@ -1251,7 +1251,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-94100</v>
+        <v>-98500</v>
       </c>
       <c r="E20" s="3">
         <v>-93800</v>
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1784500</v>
+        <v>1788900</v>
       </c>
       <c r="E21" s="3">
         <v>909100</v>
@@ -1863,7 +1863,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>94100</v>
+        <v>98500</v>
       </c>
       <c r="E32" s="3">
         <v>93800</v>
